--- a/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="301" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="307" uniqueCount="124">
   <si>
     <t>field</t>
   </si>
@@ -27,10 +27,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Target year</t>
-  </si>
-  <si>
-    <t>Baseline period</t>
+    <t>Output type</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Surveillance area</t>
   </si>
   <si>
     <t>Registry</t>
@@ -39,6 +42,12 @@
     <t>Geography</t>
   </si>
   <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Release date</t>
+  </si>
+  <si>
     <t>Contents</t>
   </si>
   <si>
@@ -54,28 +63,37 @@
     <t>cvd_case_fatality_2023_v1</t>
   </si>
   <si>
-    <t>Hospital cardiovascular case-fatality in Barbados, 2023</t>
+    <t>CVD case-fatality in Barbados, 2012-2023</t>
+  </si>
+  <si>
+    <t>briefing</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>CVD</t>
+  </si>
+  <si>
+    <t>BNR-CVD</t>
+  </si>
+  <si>
+    <t>Barbados</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2018-2022</t>
-  </si>
-  <si>
-    <t>BNR-CVD</t>
-  </si>
-  <si>
-    <t>Barbados</t>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
   </si>
   <si>
-    <t>Aggregate hospital-ascertained case counts</t>
-  </si>
-  <si>
-    <t>Case-fatality based on hospital cases</t>
+    <t>Aggregate case-fatality estimates for hospital-ascertained CVD cases.</t>
+  </si>
+  <si>
+    <t>Case-fatality based on hospital-ascertained cases only.</t>
   </si>
   <si>
     <t>etype</t>
@@ -415,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,7 +441,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -431,7 +449,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -439,7 +457,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +465,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -455,7 +473,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -463,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -471,7 +489,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -479,7 +497,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -487,7 +505,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -495,7 +513,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -509,66 +551,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1">
         <v>427</v>
@@ -615,13 +657,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1">
         <v>480</v>
@@ -668,13 +710,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1">
         <v>515</v>
@@ -721,13 +763,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1">
         <v>589</v>
@@ -774,13 +816,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1">
         <v>596</v>
@@ -827,13 +869,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1">
         <v>551</v>
@@ -880,13 +922,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>598</v>
@@ -933,13 +975,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1">
         <v>387</v>
@@ -986,13 +1028,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1">
         <v>461</v>
@@ -1039,13 +1081,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1">
         <v>450</v>
@@ -1092,13 +1134,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1">
         <v>518</v>
@@ -1145,13 +1187,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1">
         <v>576</v>
@@ -1198,13 +1240,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1">
         <v>541</v>
@@ -1251,13 +1293,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1">
         <v>595</v>
@@ -1304,13 +1346,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1">
         <v>105</v>
@@ -1357,13 +1399,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1">
         <v>160</v>
@@ -1410,13 +1452,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" s="1">
         <v>209</v>
@@ -1463,13 +1505,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1">
         <v>226</v>
@@ -1516,13 +1558,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
         <v>257</v>
@@ -1569,13 +1611,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D21" s="1">
         <v>214</v>
@@ -1622,13 +1664,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D22" s="1">
         <v>210</v>
@@ -1675,13 +1717,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D23" s="1">
         <v>140</v>
@@ -1728,13 +1770,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1">
         <v>180</v>
@@ -1781,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1">
         <v>236</v>
@@ -1834,13 +1876,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1">
         <v>269</v>
@@ -1887,13 +1929,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1">
         <v>311</v>
@@ -1940,13 +1982,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D28" s="1">
         <v>278</v>
@@ -1993,13 +2035,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D29" s="1">
         <v>276</v>
@@ -2055,200 +2097,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2262,416 +2304,416 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
         <v>101</v>
-      </c>
-      <c r="G6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
@@ -84,7 +84,7 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2026-05-15</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
@@ -243,9 +243,6 @@
     <t>v1</t>
   </si>
   <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
     <t>Ian Hambleton, Analyst</t>
   </si>
   <si>
@@ -276,7 +273,7 @@
     <t>CC BY 4.0 Attribution</t>
   </si>
   <si>
-    <t>Barbados National Registry approved cardiovascular registry extract (Jan 2010-Dec 2023)</t>
+    <t>bnr_cvd_input_case_fatality_202401_v01</t>
   </si>
   <si>
     <t>Barbados National Registry</t>
@@ -291,18 +288,21 @@
     <t>float</t>
   </si>
   <si>
+    <t>byte</t>
+  </si>
+  <si>
     <t>double</t>
   </si>
   <si>
     <t>display_format</t>
   </si>
   <si>
+    <t>%8.0g</t>
+  </si>
+  <si>
     <t>%9.0g</t>
   </si>
   <si>
-    <t>%8.0g</t>
-  </si>
-  <si>
     <t>%4.1f</t>
   </si>
   <si>
@@ -327,13 +327,13 @@
     <t>variable_label</t>
   </si>
   <si>
-    <t>CVD Event Type (AMI=2, Stroke=1)</t>
-  </si>
-  <si>
-    <t>Patient sex (1=female, 2=male)</t>
-  </si>
-  <si>
-    <t>Two year intervals between 2010 and 2023</t>
+    <t>CVD event type</t>
+  </si>
+  <si>
+    <t>Sex at birth</t>
+  </si>
+  <si>
+    <t>Two-year intervals between 2010 and 2023</t>
   </si>
   <si>
     <t>Number of events</t>
@@ -387,7 +387,7 @@
     <t xml:space="preserve">1=Female; 2=Male; </t>
   </si>
   <si>
-    <t xml:space="preserve">1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; 8=2010-2011; 9=2012-2013; 10=2014-2015; 11=2016-2017; 12=2018-2019; 13=2020-2021; </t>
+    <t xml:space="preserve">1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; 8=2012-2013; 9=2014-2015; 10=2016-2017; 11=2018-2019; 12=2020-2021; 13=2022-2023; </t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1405,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1">
         <v>160</v>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1">
         <v>209</v>
@@ -1511,7 +1511,7 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1">
         <v>226</v>
@@ -1564,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" s="1">
         <v>257</v>
@@ -1617,7 +1617,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="1">
         <v>214</v>
@@ -1670,7 +1670,7 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1">
         <v>210</v>
@@ -1776,7 +1776,7 @@
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="1">
         <v>180</v>
@@ -1829,7 +1829,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" s="1">
         <v>236</v>
@@ -1882,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1">
         <v>269</v>
@@ -1935,7 +1935,7 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" s="1">
         <v>311</v>
@@ -1988,7 +1988,7 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28" s="1">
         <v>278</v>
@@ -2041,7 +2041,7 @@
         <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="1">
         <v>276</v>
@@ -2136,7 +2136,7 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -2147,7 +2147,7 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -2169,7 +2169,7 @@
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -2180,7 +2180,7 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -2191,7 +2191,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -2213,7 +2213,7 @@
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -2224,7 +2224,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -2235,7 +2235,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -2246,7 +2246,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -2257,7 +2257,7 @@
         <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -2268,7 +2268,7 @@
         <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -2279,7 +2279,7 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -2290,7 +2290,7 @@
         <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2307,10 +2307,10 @@
         <v>54</v>
       </c>
       <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" t="s">
-        <v>89</v>
       </c>
       <c r="D1" t="s">
         <v>92</v>
@@ -2333,7 +2333,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -2359,7 +2359,7 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>99</v>
@@ -2379,10 +2379,10 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>100</v>
@@ -2405,7 +2405,7 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>101</v>
@@ -2428,7 +2428,7 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>101</v>
@@ -2451,7 +2451,7 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>101</v>
@@ -2474,7 +2474,7 @@
         <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>101</v>
@@ -2497,7 +2497,7 @@
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>101</v>
@@ -2520,7 +2520,7 @@
         <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>101</v>
@@ -2540,7 +2540,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -2563,7 +2563,7 @@
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
         <v>95</v>
@@ -2586,7 +2586,7 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>96</v>
@@ -2609,7 +2609,7 @@
         <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>96</v>
@@ -2632,7 +2632,7 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -2655,7 +2655,7 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>96</v>
@@ -2678,7 +2678,7 @@
         <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -2701,7 +2701,7 @@
         <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>96</v>

--- a/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
+++ b/site/downloads/files/briefings/cvd_case_fatality_2023_v1/workbook/bnr_cvd_case_fatality_2023_v1.xlsx
@@ -84,7 +84,7 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2026-08-07</t>
+    <t>2026-08-13</t>
   </si>
   <si>
     <t>Data sheets, dataset metadata sheets, and variable metadata sheets</t>
@@ -387,7 +387,7 @@
     <t xml:space="preserve">1=Female; 2=Male; </t>
   </si>
   <si>
-    <t xml:space="preserve">1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; 8=2012-2013; 9=2014-2015; 10=2016-2017; 11=2018-2019; 12=2020-2021; 13=2022-2023; </t>
+    <t xml:space="preserve">1=2010-2011; 2=2012-2013; 3=2014-2015; 4=2016-2017; 5=2018-2019; 6=2020-2021; 7=2022-2023; </t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1352,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <v>105</v>
@@ -1723,7 +1723,7 @@
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1">
         <v>140</v>
